--- a/naver-place-crawler/results_nail/대구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/대구_네일샵.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -628,10 +628,10 @@
         <v>804</v>
       </c>
       <c r="Q2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R2" t="n">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>대구 갓네일 만촌점</t>
+          <t>채희뷰티 침산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>keoyeon_s@naver.com</t>
+          <t>chaehyejung1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1341-5077</t>
+          <t>0507-1359-0318</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구 수성구 달구벌대로 2583 월드메르디앙 1층 상가</t>
+          <t>대구 북구 고성로 142 3층 301호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://naver.me/FvEwBTon</t>
+          <t>https://www.instagram.com/chaehee_beauty_sol</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tid0</t>
+          <t>https://talk.naver.com/ct/wygrx80</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2698</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>262</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2960</v>
+        <v>10</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1915071085</t>
+          <t>2020966033</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1915071085</t>
+          <t>https://m.place.naver.com/place/2020966033</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>예뻐질곧 네일 동성로점</t>
+          <t>대구 갓네일 만촌점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>udts12@naver.com</t>
+          <t>keoyeon_s@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1331-8889</t>
+          <t>0507-1341-5077</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 중구 공평로 18 1층</t>
+          <t>대구 수성구 달구벌대로 2583 월드메르디앙 1층 상가</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/udts12</t>
+          <t>https://naver.me/FvEwBTon</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcem8m</t>
+          <t>https://talk.naver.com/ct/w5tid0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2050</v>
+        <v>2698</v>
       </c>
       <c r="Q4" t="n">
-        <v>439</v>
+        <v>262</v>
       </c>
       <c r="R4" t="n">
-        <v>2489</v>
+        <v>2960</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1371136292</t>
+          <t>1915071085</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1371136292</t>
+          <t>https://m.place.naver.com/place/1915071085</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>갓네일 범어점</t>
+          <t>예뻐질곧 네일 동성로점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>god_nail_2000@naver.com</t>
+          <t>udts12@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1381-6116</t>
+          <t>0507-1331-8889</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 상가 2층 갓네일 범어점</t>
+          <t>대구 중구 공평로 18 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/god_nail_2000</t>
+          <t>https://blog.naver.com/udts12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4l6kg</t>
+          <t>https://talk.naver.com/ct/wcem8m</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>5958</v>
+        <v>2050</v>
       </c>
       <c r="Q5" t="n">
-        <v>497</v>
+        <v>440</v>
       </c>
       <c r="R5" t="n">
-        <v>6455</v>
+        <v>2490</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1939513552</t>
+          <t>1371136292</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1939513552</t>
+          <t>https://m.place.naver.com/place/1371136292</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>유지네일</t>
+          <t>갓네일 범어점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>yyi1261@naver.com</t>
+          <t>god_nail_2000@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1446-2883</t>
+          <t>0507-1381-6116</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구 중구 동성로2길 18-1 유지네일</t>
+          <t>대구 수성구 상록로 15 상가 2층 갓네일 범어점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/me/Yuzi2882</t>
+          <t>https://blog.naver.com/god_nail_2000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfb9hfd</t>
+          <t>https://talk.naver.com/ct/w4l6kg</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>385</v>
+        <v>5960</v>
       </c>
       <c r="Q6" t="n">
-        <v>1866</v>
+        <v>497</v>
       </c>
       <c r="R6" t="n">
-        <v>2251</v>
+        <v>6457</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1145326202</t>
+          <t>1939513552</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145326202</t>
+          <t>https://m.place.naver.com/place/1939513552</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>욥네일</t>
+          <t>유지네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>real1jh@naver.com</t>
+          <t>yyi1261@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1308-9675</t>
+          <t>0507-1446-2883</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 서구 평리로52길 30 1층</t>
+          <t>대구 중구 동성로2길 18-1 유지네일</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_eFSxmG</t>
+          <t>https://open.kakao.com/me/Yuzi2882</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5iu23</t>
+          <t>https://talk.naver.com/ct/wfb9hfd</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>201</v>
+        <v>385</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1867</v>
       </c>
       <c r="R7" t="n">
-        <v>201</v>
+        <v>2252</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1176650506</t>
+          <t>1145326202</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176650506</t>
+          <t>https://m.place.naver.com/place/1145326202</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엔케어센터 대구동인점</t>
+          <t>엔피케어 대구남구점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ahgeurina@naver.com</t>
+          <t>np_care@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1417-0856</t>
+          <t>0507-1315-8125</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 중구 동덕로36길 15 2층 엔케어센터 대구동인점</t>
+          <t>대구 남구 명덕로 334 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/agrina_nail</t>
+          <t>https://www.youtube.com/@NPCARE_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4s329</t>
+          <t>https://talk.naver.com/ct/w45dxp</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>554</v>
+        <v>497</v>
       </c>
       <c r="Q8" t="n">
-        <v>536</v>
+        <v>107</v>
       </c>
       <c r="R8" t="n">
-        <v>1090</v>
+        <v>604</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1224287095</t>
+          <t>1319918465</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224287095</t>
+          <t>https://m.place.naver.com/place/1319918465</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>니가반한뷰티 율하 본점</t>
+          <t>루멘네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sbk728@naver.com</t>
+          <t>lumen_nail@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1315-3806</t>
+          <t>0507-1423-2436</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 동구 안심로7길 7 율하역 엘크루 아파트 상가 1층 103동 108호</t>
+          <t>대구 달서구 달구벌대로 1530 삼정브리티시몰 상가 3층 314호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://instagram.com/ni_ban_view</t>
+          <t>https://blog.naver.com/lumen_nail</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wviv4d6</t>
+          <t>https://talk.naver.com/ct/wj2mo2f</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>54</v>
+        <v>1162</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="R9" t="n">
-        <v>65</v>
+        <v>1205</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1172172767</t>
+          <t>1735360442</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1172172767</t>
+          <t>https://m.place.naver.com/place/1735360442</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>루멘네일</t>
+          <t>클린풋네일&amp;베어푸스플레게 문제성 무좀 내성 발톱 발각질</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lumen_nail@naver.com</t>
+          <t>jhj6499@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1423-2436</t>
+          <t>0507-1420-5879</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 달서구 달구벌대로 1530 삼정브리티시몰 상가 3층 314호</t>
+          <t>대구 서구 통학로 13 1층 102호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lumen_nail</t>
+          <t>https://www.instagram.com/haehr_cleanfoot</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wj2mo2f</t>
+          <t>https://talk.naver.com/ct/wcbvq3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1162</v>
+        <v>360</v>
       </c>
       <c r="Q10" t="n">
-        <v>43</v>
+        <v>257</v>
       </c>
       <c r="R10" t="n">
-        <v>1205</v>
+        <v>617</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1735360442</t>
+          <t>34308943</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735360442</t>
+          <t>https://m.place.naver.com/place/34308943</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일라헨느</t>
+          <t>푸스원 \u002F 내성발톱 발톱무좀 발각질 티눈</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tjwlgus553@naver.com</t>
+          <t>fusslab2228@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1320-8536</t>
+          <t>0507-1349-2228</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 수성구 무학로21안길 14 1층 네일 라헨느</t>
+          <t>대구 수성구 달구벌대로496길 19-4 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_la_reine?igsh=bm41NTA0Mjh1bHZr</t>
+          <t>https://blog.naver.com/fusslab2228</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tsid</t>
+          <t>https://talk.naver.com/ct/wcjz301</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="Q11" t="n">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="R11" t="n">
-        <v>456</v>
+        <v>199</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1209908309</t>
+          <t>2026933809</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209908309</t>
+          <t>https://m.place.naver.com/place/2026933809</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
